--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260307_201515.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260307_201515.xlsx
@@ -3916,7 +3916,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
